--- a/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/nov-2025.xlsx
+++ b/docs/oc-mensuales/desarrollo-y-mantencion-de-software-ti-e-iaas/nov-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>570.58</v>
+        <v>24170.57</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>859.806</v>
+        <v>36422.6</v>
       </c>
     </row>
     <row r="4">
@@ -687,17 +687,17 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>619.9194</v>
+        <v>26260.66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5520-10581-CM25</t>
+          <t>875-170-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.720.000-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Agencia de Promocion de la inversion extranjera</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,28 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7654.4</v>
+        <v>6973.11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>875-170-CM25</t>
+          <t>699360-124-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.720.000-9</t>
+          <t>60.505.000-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agencia de Promocion de la inversion extranjera</t>
+          <t>Dirección General de Carabineros de Chile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,28 +798,28 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>Geosolve Cia Ltda</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>76.562.690-0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>164.61</v>
+        <v>25190.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>699360-124-CM25</t>
+          <t>5401-5-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,43 +844,43 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.505.000-k</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>Servicio de Salud del Maule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Geosolve Cia Ltda</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.562.690-0</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>594.664</v>
+        <v>34153.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5401-5-CM25</t>
+          <t>612-4428-SE25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,37 +905,41 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Maule</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>SERVICIOS INFORMATICOS GOVMS SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>76.384.526-5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>806.2488</v>
+        <v>41084.21</v>
       </c>
     </row>
     <row r="9">
@@ -992,17 +996,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>205.3408</v>
+        <v>8698.530000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>612-4428-SE25</t>
+          <t>730566-409-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1027,12 +1031,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,26 +1046,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS GOVMS SPA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.384.526-5</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>77.436.870-1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>969.85</v>
+        <v>174867.91</v>
       </c>
     </row>
     <row r="11">
@@ -1118,17 +1118,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>446.8464</v>
+        <v>18929.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>730566-409-CM25</t>
+          <t>1314-61-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,28 +1168,28 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4128</v>
+        <v>20973.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1314-61-CM25</t>
+          <t>1314-63-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1229,28 +1229,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>495.1127</v>
+        <v>15963.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1314-63-CM25</t>
+          <t>1602-157-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1270,17 +1270,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,28 +1290,28 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>KLEINROCK SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>77.146.212-K</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>376.836</v>
+        <v>9376.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1602-157-CM25</t>
+          <t>1725-5837-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1336,43 +1336,43 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KLEINROCK SPA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.146.212-K</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>221.34</v>
+        <v>9849.030000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1725-5837-CM25</t>
+          <t>2432-1045-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,48 +1392,48 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.254.300-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>SOLNET SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.723.130-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>232.5</v>
+        <v>33256.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2432-1045-CM25</t>
+          <t>1725-5863-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1448,53 +1448,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.254.300-9</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD ESTACION CENTRAL</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOLNET SPA</t>
+          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.723.130-4</t>
+          <t>76.185.219-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>785.061</v>
+        <v>6913.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1725-5863-CM25</t>
+          <t>2719-4296-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1514,48 +1514,48 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.072.200-3</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE PIRQUE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SERVICIOS INFORMATICOS ACTIS LIMITADA</t>
+          <t>MT2 SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.185.219-1</t>
+          <t>76.967.524-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>163.2057</v>
+        <v>26179.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2719-4296-CM25</t>
+          <t>45-389-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1575,17 +1575,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.072.200-3</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PIRQUE</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,22 +1595,22 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MT2 SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.967.524-8</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>618.0036</v>
+        <v>11916.27</v>
       </c>
     </row>
     <row r="20">
@@ -1667,17 +1667,17 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1196.98</v>
+        <v>50705.76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45-389-CM25</t>
+          <t>918434-450-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.980.680-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,28 +1717,28 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>281.3</v>
+        <v>173495.42</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>918434-450-CM25</t>
+          <t>1469-3580-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1758,48 +1758,48 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.980.680-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE LA MUJER Y LA EQUIDAD DE GÉNERO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>DATCO CHILE S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>96.897.630-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4095.6006</v>
+        <v>48598.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1469-3580-CM25</t>
+          <t>1314-62-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,43 +1824,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DATCO CHILE S A</t>
+          <t>Tecnova</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.897.630-3</t>
+          <t>77.430.680-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1147.24</v>
+        <v>20487.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1314-62-CM25</t>
+          <t>1368-125-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>75.980.060-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,28 +1900,28 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Tecnova</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.430.680-3</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>483.6279</v>
+        <v>18314.71</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1368-125-CM25</t>
+          <t>1422825-2004-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1946,43 +1946,43 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>75.980.060-5</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CORPORACIÓN DE FOMENTO DE LA PRODUCCIÓN - CORFO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>SERVICIOS INTERNET LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>77.409.600-0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>432.3442</v>
+        <v>50566.84</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1422825-2004-CM25</t>
+          <t>45-424-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2002,48 +2002,48 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SERVICIOS INTERNET LIMITADA</t>
+          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.409.600-0</t>
+          <t>76.153.158-1</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1193.7006</v>
+        <v>10823.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45-424-CM25</t>
+          <t>4467-12-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,28 +2083,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Comercial y Servicios de Ingeniería AYD Limitada</t>
+          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.153.158-1</t>
+          <t>76.011.651-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>255.4989</v>
+        <v>23637.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4467-12-CM25</t>
+          <t>14-584-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,28 +2144,28 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ASESORIAS COGNUS CONSULTING S.A.</t>
+          <t>COMPUNET S.P.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.011.651-3</t>
+          <t>78.466.220-9</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>558</v>
+        <v>7624.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>14-584-CM25</t>
+          <t>1057501-31291-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,28 +2205,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMPUNET S.P.A.</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.466.220-9</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>179.9765</v>
+        <v>60187.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057501-31291-CM25</t>
+          <t>45-437-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,28 +2266,28 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1420.8</v>
+        <v>23913.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>45-437-CM25</t>
+          <t>1093219-12-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,28 +2327,28 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Seidor Chile S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.986.170-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>564.51</v>
+        <v>34566.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4754-2-CM25</t>
+          <t>316-791-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2368,48 +2368,48 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.901.000-2</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MCL CONSULTING</t>
+          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.314.701-0</t>
+          <t>79.560.740-4</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>443.94</v>
+        <v>530554.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1093219-12-CM25</t>
+          <t>4754-2-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.901.000-2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2449,28 +2449,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Seidor Chile S.A.</t>
+          <t>MCL CONSULTING</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>96.986.170-4</t>
+          <t>76.314.701-0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>816</v>
+        <v>18805.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>316-791-CM25</t>
+          <t>1591-382-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2485,53 +2485,53 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INGENIERIA Y SISTEMAS COMPUTACIONALES S.A.</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>79.560.740-4</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12524.477</v>
+        <v>49700.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1591-382-CM25</t>
+          <t>599-436-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2571,28 +2571,28 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.554.706-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1173.25</v>
+        <v>41681.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>599-436-CM25</t>
+          <t>1375757-79-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.981.240-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2632,28 +2632,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>ULLOA Y TORO CONSULTORES ASOCIADOS SPA</t>
+          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.554.706-7</t>
+          <t>76.522.707-0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>983.9400000000001</v>
+        <v>20363.13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1375757-79-CM25</t>
+          <t>1591-377-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.981.240-9</t>
+          <t>60.704.000-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA PUELCHE</t>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2693,28 +2693,28 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>CONSULTORA, CHERRIE PIZARRO SANTOS EMPRESA INDIVIDUAL DE RESPONSABILID</t>
+          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.522.707-0</t>
+          <t>76.232.892-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>480.7</v>
+        <v>16144.78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1591-377-CM25</t>
+          <t>1314-47-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2729,22 +2729,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.704.000-1</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,28 +2754,28 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SOFTLINE INTERNATIONAL CHILE SPA</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.232.892-5</t>
+          <t>76.348.639-7</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>381.12</v>
+        <v>47796.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1314-47-CM25</t>
+          <t>1111089-481-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,28 +2815,28 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1128.3049</v>
+        <v>14340.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1111089-481-CM25</t>
+          <t>608897-11302-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2856,17 +2856,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2876,28 +2876,28 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>CONCORDIA SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.751.321-6</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>338.5386</v>
+        <v>40203.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>608897-11302-CM25</t>
+          <t>45-443-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2937,28 +2937,28 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CONCORDIA SPA</t>
+          <t>ANDES DIGITAL</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.751.321-6</t>
+          <t>76.975.787-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>949.05</v>
+        <v>26395.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>45-443-CM25</t>
+          <t>587-654-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>61.801.000-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2998,28 +2998,28 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ANDES DIGITAL</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.975.787-2</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>623.1</v>
+        <v>32041.65</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>587-654-CM25</t>
+          <t>2580-1226-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.801.000-7</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3059,28 +3059,28 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>756.3876</v>
+        <v>743345.55</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2580-1226-CM25</t>
+          <t>1605-404-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.803.000-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3120,28 +3120,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>Servicos Integrados en Información Geográfica S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>96.777.670-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>17547.705</v>
+        <v>153592.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1605-404-CM25</t>
+          <t>612-4351-SE25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>60.803.000-K</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3181,28 +3181,32 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Servicos Integrados en Información Geográfica S.A.</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.777.670-k</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.733.311-9</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>3625.7585</v>
+        <v>323226.04</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>612-4351-SE25</t>
+          <t>1314-66-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3222,17 +3226,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3242,32 +3246,28 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>RIALIS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.348.639-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7630.2</v>
+        <v>20384.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1314-66-CM25</t>
+          <t>1153624-267-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3287,17 +3287,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3307,28 +3307,28 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>RIALIS SPA</t>
+          <t>INVERSIONES ENVISION CL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.348.639-7</t>
+          <t>77.733.311-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>481.2088</v>
+        <v>9898.27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1153624-267-CM25</t>
+          <t>730566-562-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3368,28 +3368,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>INVERSIONES ENVISION CL SPA</t>
+          <t>FERNANDO MARCELO</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.733.311-9</t>
+          <t>76.811.563-K</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>233.6625</v>
+        <v>19934.43</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>730566-562-CM25</t>
+          <t>730566-563-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3440,17 +3440,17 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>470.58</v>
+        <v>34490.66</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>730566-563-CM25</t>
+          <t>1057402-36569-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3475,43 +3475,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>FERNANDO MARCELO</t>
+          <t>GEORG</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.811.563-K</t>
+          <t>76.624.276-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>814.2</v>
+        <v>24031.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057402-36569-CM25</t>
+          <t>1177296-517-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3531,48 +3531,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>GEORG</t>
+          <t>INGENIERÍA TICMEGA SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.624.276-6</t>
+          <t>76.516.342-0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>567.3</v>
+        <v>20496.15</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1177296-517-CM25</t>
+          <t>1057491-16211-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3587,22 +3587,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3612,28 +3612,28 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>INGENIERÍA TICMEGA SPA</t>
+          <t>Transaction Line Chile S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.516.342-0</t>
+          <t>76.300.290-K</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>483.84</v>
+        <v>6913.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057491-16211-CM25</t>
+          <t>1314-68-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,28 +3673,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transaction Line Chile S.A.</t>
+          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.300.290-K</t>
+          <t>77.077.350-4</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>163.2018</v>
+        <v>19472.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1314-68-CM25</t>
+          <t>757-293-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3709,22 +3709,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.601.000-k</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3734,28 +3734,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>NEURONET SOLUCIONES DE INGENIERIA Y TECNOLOGIA S.A.</t>
+          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.077.350-4</t>
+          <t>76.444.489-2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>459.6711</v>
+        <v>52612.87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>757-293-CM25</t>
+          <t>1111089-522-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.601.000-k</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3795,28 +3795,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EVOLUCION, TRANSFORMACION Y CAMBIO CONSULTORES SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.444.489-2</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1242</v>
+        <v>340882.62</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1111089-522-CM25</t>
+          <t>5403-70-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>61.978.810-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>COMISION NACIONAL DE ACREDITACION</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3856,28 +3856,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>CODER HUB SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.734.221-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8047.008</v>
+        <v>53509.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5403-70-CM25</t>
+          <t>519302-164-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3897,17 +3897,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.978.810-9</t>
+          <t>65.999.669-3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE ACREDITACION</t>
+          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3917,28 +3917,28 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>CODER HUB SPA</t>
+          <t>APIUX TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.734.221-7</t>
+          <t>76.516.485-0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1263.16</v>
+        <v>20757.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>519302-164-CM25</t>
+          <t>586-630-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3963,43 +3963,43 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65.999.669-3</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE PROPIEDAD INDUSTRIAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>APIUX TECNOLOGIA SPA</t>
+          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.516.485-0</t>
+          <t>76.130.712-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>490</v>
+        <v>531687.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>586-630-CM25</t>
+          <t>756-508-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4024,43 +4024,43 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TIVIT CHILE TERCERIZACION DE PROCESOS, SERVICIOS Y TECNOLOGIA SPA</t>
+          <t>INFO-UPDATE LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.130.712-6</t>
+          <t>76.023.530-k</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12551.2283</v>
+        <v>13013.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>756-508-CM25</t>
+          <t>1436381-48-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMA</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4100,28 +4100,28 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>INFO-UPDATE LIMITADA</t>
+          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.023.530-k</t>
+          <t>76.198.095-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>307.2</v>
+        <v>20757.09</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1436381-48-CM25</t>
+          <t>730566-569-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.980.240-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4161,28 +4161,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CORTES, MONCADA Y PIZARRO LIMITADA</t>
+          <t>VISIION LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.198.095-5</t>
+          <t>77.436.870-1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>490</v>
+        <v>67799.44</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>730566-569-CM25</t>
+          <t>1314-65-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4197,22 +4197,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.980.240-3</t>
+          <t>60.706.000-2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE EVALUACION SOCIAL</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4222,28 +4222,28 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>VISIION LTDA</t>
+          <t>Adevcom ltda</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>77.436.870-1</t>
+          <t>76.460.930-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1600.5</v>
+        <v>20257.65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1314-65-CM25</t>
+          <t>611669-379-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>60.706.000-2</t>
+          <t>61.979.950-k</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>Superintendencia del Medio Ambiente</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4283,28 +4283,28 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Adevcom ltda</t>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.460.930-1</t>
+          <t>77.754.348-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>478.21</v>
+        <v>15364.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>611669-379-CM25</t>
+          <t>1057417-41801-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4324,48 +4324,48 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.979.950-k</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Superintendencia del Medio Ambiente</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>77.592.300-8</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>362.7</v>
+        <v>7352.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057417-41801-CM25</t>
+          <t>585-245-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4390,43 +4390,43 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ANALYZE CONSULTORIA Y DESARROLLO SPA</t>
+          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.592.300-8</t>
+          <t>76.304.354-1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>173.5776</v>
+        <v>54900.39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>585-245-CM25</t>
+          <t>2777-884-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4451,43 +4451,43 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>CONSULTORIA INFORMATICA CUNIX LIMITADA</t>
+          <t>RAYEN SALUD SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.304.354-1</t>
+          <t>77.917.240-6</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1296</v>
+        <v>153872.05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2777-884-CM25</t>
+          <t>585-246-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4512,43 +4512,43 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>RAYEN SALUD SPA</t>
+          <t>INNOVA TECNOLOGIAS DE LA INFORMACION SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.917.240-6</t>
+          <t>76.058.901-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3632.3636</v>
+        <v>14903.55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>585-246-CM25</t>
+          <t>1172835-1-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4568,17 +4568,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.109.000-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4588,28 +4588,28 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>INNOVA TECNOLOGIAS DE LA INFORMACION SPA</t>
+          <t>SAARGO SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.058.901-2</t>
+          <t>76.891.821-k</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>351.819</v>
+        <v>7682.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1172835-1-CM25</t>
+          <t>711-634-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.109.000-7</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4649,28 +4649,28 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SAARGO SPA</t>
+          <t>INFORMATICA Y SISTEMAS COMPUTACIONALES ORBIS LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.891.821-k</t>
+          <t>77.758.914-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>181.35</v>
+        <v>34256.39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>711-634-CM25</t>
+          <t>721-354-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4710,28 +4710,28 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>INFORMATICA Y SISTEMAS COMPUTACIONALES ORBIS LIMITADA</t>
+          <t>Transaction Line Chile S.A.</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>77.758.914-8</t>
+          <t>76.300.290-K</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>808.6695999999999</v>
+        <v>14852.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>721-354-CM25</t>
+          <t>3756-813-SE25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4751,107 +4751,46 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transaction Line Chile S.A.</t>
+          <t>SOCIEDAD ONE CONSULTORES SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.300.290-K</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.286.397-9</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>350.61</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>3756-813-SE25</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2239-19-LR23</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>nov-2025</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>69.110.600-4</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>SOCIEDAD ONE CONSULTORES SPA</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>76.286.397-9</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>CLF</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>748.55</v>
+        <v>31709.63</v>
       </c>
     </row>
   </sheetData>
